--- a/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,7 +367,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1575,7 +1575,7 @@
     <t>streetName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1591,7 +1591,7 @@
     <t>houseNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1607,7 +1607,7 @@
     <t>unitID</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-unitID|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-unitID|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1656,7 +1656,7 @@
     <t>postOfficeBoxNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-postBox|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-postBox|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1869,7 +1869,7 @@
     <t>countrycode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-SC-coding|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-codedString|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1916,7 +1916,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1992,7 +1992,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -2063,7 +2063,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -14552,7 +14552,7 @@
         <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>139</v>
@@ -14669,7 +14669,7 @@
         <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>139</v>
@@ -14786,7 +14786,7 @@
         <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>139</v>
@@ -15597,7 +15597,7 @@
         <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>139</v>
@@ -17096,7 +17096,7 @@
         <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>596</v>

--- a/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-organization-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
